--- a/excell/documents.xlsx
+++ b/excell/documents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0F268D-0482-455F-A54A-78C8A742B212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8709C559-EF7E-4D93-88D1-2E317CD3A148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4985E1F7-F929-4799-84E2-2425739985C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>Type</t>
   </si>
@@ -56,15 +56,6 @@
     <t>pdf</t>
   </si>
   <si>
-    <t>Bylaws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MWSCAS  Steering Committee Bylaws Update </t>
-  </si>
-  <si>
-    <t>bylaws.pdf</t>
-  </si>
-  <si>
     <t>MWSCAS SC Agenda</t>
   </si>
   <si>
@@ -110,22 +101,43 @@
     <t>minutes2025.pdf</t>
   </si>
   <si>
-    <t>Jennifer Blain nomination of Sahil Shah for the Steering Committee</t>
-  </si>
-  <si>
-    <t>nomination_sahil.pdf</t>
-  </si>
-  <si>
-    <t>Sahil Shah Nomination</t>
-  </si>
-  <si>
-    <t>CV of Sahil Shah to support his nomination to the Steering Committee</t>
-  </si>
-  <si>
-    <t>sahil_cv.pdf</t>
-  </si>
-  <si>
-    <t>Sahil Shah CV</t>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Note:  Anyone can download public documents.  Member's Only documents are encrypted and require a pin number to download.</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>Image Test</t>
+  </si>
+  <si>
+    <t>Display jpg image</t>
+  </si>
+  <si>
+    <t>mwscas_logo.jpg</t>
+  </si>
+  <si>
+    <t>The final report of the MWSCAS 2025 committee</t>
+  </si>
+  <si>
+    <t>otr</t>
+  </si>
+  <si>
+    <t>MWSCAS2025_Awards_Slides.pptx</t>
+  </si>
+  <si>
+    <t>MWSCAS 2025 Awards</t>
   </si>
 </sst>
 </file>
@@ -497,15 +509,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC7F305-EF14-4449-A820-8F7D08EA7884}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="56.81640625" customWidth="1"/>
-    <col min="4" max="4" width="24.08984375" customWidth="1"/>
+    <col min="3" max="3" width="104.453125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -518,117 +530,135 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/excell/documents.xlsx
+++ b/excell/documents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8709C559-EF7E-4D93-88D1-2E317CD3A148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE9FEBD-7CBE-4401-8EB6-4F459E43D8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4985E1F7-F929-4799-84E2-2425739985C0}"/>
   </bookViews>
@@ -65,12 +65,6 @@
     <t>agenda2026.pdf</t>
   </si>
   <si>
-    <t>Treasurer's Report 2026</t>
-  </si>
-  <si>
-    <t>The 2026 Treasurer's Report to the MWSCAS Steering Committee</t>
-  </si>
-  <si>
     <t>treasurers_report_2026.pdf</t>
   </si>
   <si>
@@ -116,18 +110,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>img</t>
-  </si>
-  <si>
-    <t>Image Test</t>
-  </si>
-  <si>
-    <t>Display jpg image</t>
-  </si>
-  <si>
-    <t>mwscas_logo.jpg</t>
-  </si>
-  <si>
     <t>The final report of the MWSCAS 2025 committee</t>
   </si>
   <si>
@@ -138,6 +120,24 @@
   </si>
   <si>
     <t>MWSCAS 2025 Awards</t>
+  </si>
+  <si>
+    <t>Finance Report 2026</t>
+  </si>
+  <si>
+    <t>The 2026 Report of the Finance Committee to the MWSCAS Steering Committee</t>
+  </si>
+  <si>
+    <t>htm</t>
+  </si>
+  <si>
+    <t>Activity Report</t>
+  </si>
+  <si>
+    <t>Steering Committee members need to look carefully at their own entry on this activity report and provide any updates needed to Michael Soderstrand at soderstrand@ieee.org</t>
+  </si>
+  <si>
+    <t>activity_report.html</t>
   </si>
 </sst>
 </file>
@@ -513,7 +513,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="104.453125" customWidth="1"/>
+    <col min="3" max="3" width="139.26953125" customWidth="1"/>
     <col min="4" max="4" width="30.90625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -531,15 +531,15 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -564,16 +564,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -581,16 +581,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -598,16 +598,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -615,50 +615,50 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
